--- a/public/downloads/lead-magnets/checklist-fidelizacao-30-dias.xlsx
+++ b/public/downloads/lead-magnets/checklist-fidelizacao-30-dias.xlsx
@@ -8,14 +8,16 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Leia primeiro" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Plano 30 dias" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Comece aqui" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Painel rápido" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Plano 30 dias" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Leia primeiro'!$A$1:$F$15</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Plano 30 dias'!$A$1:$I$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Plano 30 dias'!$A$1:$I$11</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Plano 30 dias'!A1:I11</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Comece aqui'!$A$1:$F$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Painel rápido'!$A$1:$I$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Plano 30 dias'!$A$1:$I$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Plano 30 dias'!$A$1:$I$11</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Plano 30 dias'!A1:I11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
-  <si>
-    <t xml:space="preserve">MATERIAL PRÁTICO FLOWO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
+  <si>
+    <t xml:space="preserve">FLOWO · MATERIAL PRÁTICO</t>
   </si>
   <si>
     <t xml:space="preserve">Checklist de fidelização — 30 dias</t>
@@ -38,25 +40,52 @@
     <t xml:space="preserve">Um ciclo simples para cuidar da experiência, planejar o retorno e aprender com as respostas dos clientes.</t>
   </si>
   <si>
-    <t xml:space="preserve">flowo.com.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMO USAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Defina uma ação útil por semana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Separe mensagens de serviço de campanhas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Registre quem executou, o resultado e pedidos de saída.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USO RESPONSÁVEL NO WHATSAPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envie mensagens de relacionamento ou oferta apenas a contatos com consentimento válido. SAIR ou PARAR interrompem divulgações. CANCELAR trata somente de um agendamento identificado e não deve, sozinho, remover o consentimento de marketing.</t>
+    <t xml:space="preserve">Veja o resumo na próxima aba. Depois, preencha somente as células rosadas e volte ao resumo para decidir o que fazer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defina uma ação útil por semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separe mensagens de serviço de campanhas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registre quem executou, o resultado e pedidos de saída.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEGENDA RÁPIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGITE AQUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATENÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células rosadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células verdes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Células amarelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHATSAPP COM RESPONSABILIDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mande ofertas somente para quem autorizou esse tipo de contato. Se a pessoa responder SAIR ou PARAR, interrompa as divulgações. CANCELAR trata apenas do agendamento informado.</t>
   </si>
   <si>
     <t xml:space="preserve">AVISO IMPORTANTE</t>
@@ -65,6 +94,54 @@
     <t xml:space="preserve">Material educativo. Adapte à realidade da sua barbearia e valide decisões contábeis, fiscais, trabalhistas e jurídicas com profissionais habilitados.</t>
   </si>
   <si>
+    <t xml:space="preserve">flowo.com.br/recursos/materiais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOWO · RESUMO SIMPLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelização em passos que cabem no mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não tente fazer tudo de uma vez: conclua a próxima ação e registre o resultado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCLUÍDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOQUEADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de 10 ações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ações que já começaram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ações que precisam de ajuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRÓXIMA AÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abra o Plano 30 dias e escolha somente a primeira ação Pendente que faz sentido para esta semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMO LER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Preencha as células rosadas nas outras abas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Volte aqui para conferir os números principais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Resolva primeiro o que estiver pendente ou bloqueado.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dia</t>
   </si>
   <si>
@@ -77,7 +154,7 @@
     <t xml:space="preserve">Tipo</t>
   </si>
   <si>
-    <t xml:space="preserve">Consentimento</t>
+    <t xml:space="preserve">Permissão para mensagem</t>
   </si>
   <si>
     <t xml:space="preserve">Responsável</t>
@@ -173,7 +250,7 @@
     <t xml:space="preserve">Contato autorizado</t>
   </si>
   <si>
-    <t xml:space="preserve">Oferecer consulta de horários a quem consentiu</t>
+    <t xml:space="preserve">Oferecer horários a quem permitiu receber mensagens</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -212,7 +289,7 @@
     <t xml:space="preserve">Inativos</t>
   </si>
   <si>
-    <t xml:space="preserve">Revisar uma única tentativa de reativação consentida</t>
+    <t xml:space="preserve">Fazer uma única tentativa com quem permitiu contato</t>
   </si>
   <si>
     <t xml:space="preserve">Resposta ou encerramento</t>
@@ -237,10 +314,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -273,15 +351,23 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="20"/>
+      <sz val="22"/>
       <color rgb="FF171810"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF6D6A61"/>
+      <color rgb="FF171810"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -301,8 +387,92 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF7A173F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F7A50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFA45D13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF171810"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC52663"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="22"/>
+      <color rgb="FF1F7A50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6D6A61"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFA45D13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF171810"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7A173F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,12 +488,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F0E5"/>
-        <bgColor rgb="FFFBF9F3"/>
+        <bgColor rgb="FFFAEEDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBF9F3"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E9EF"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F3EC"/>
+        <bgColor rgb="FFF4F0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEEDB"/>
         <bgColor rgb="FFF4F0E5"/>
       </patternFill>
     </fill>
@@ -377,7 +565,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -394,27 +582,75 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -427,11 +663,27 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF171810"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8E9EF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7A173F"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -452,6 +704,55 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA45D13"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF1F7A50"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFA45D13"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFA23030"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -466,16 +767,16 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFA45D13"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1F7A50"/>
       <rgbColor rgb="FFD9D3C6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F0E5"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFC52663"/>
+      <rgbColor rgb="FFFAEEDB"/>
+      <rgbColor rgb="FFE7F3EC"/>
+      <rgbColor rgb="FF7A173F"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
@@ -488,8 +789,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFF8E9EF"/>
+      <rgbColor rgb="FFF4F0E5"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -507,7 +808,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF171810"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFA23030"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -697,14 +998,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="18.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,7 +1014,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -724,7 +1024,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -735,136 +1035,167 @@
       <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
+    <row r="8" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="62" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="10" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="28" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="46" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="46" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="23">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
@@ -877,6 +1208,224 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="0" width="14.84"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="n">
+        <f aca="false">COUNTIF('Plano 30 dias'!$I$2:$I$11,"Concluído")</f>
+        <v>0</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14" t="n">
+        <f aca="false">COUNTIF('Plano 30 dias'!$I$2:$I$11,"Em andamento")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14" t="n">
+        <f aca="false">COUNTIF('Plano 30 dias'!$I$2:$I$11,"Bloqueado")</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -896,318 +1445,347 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="A1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="B6" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="B7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="B8" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="B10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="B11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="F11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20" t="s">
         <v>52</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I11"/>
+  <conditionalFormatting sqref="I2:I11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>ISNUMBER(SEARCH("Concluído",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>ISNUMBER(SEARCH("Publicado",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>ISNUMBER(SEARCH("Pronto",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>ISNUMBER(SEARCH("Pendente",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>ISNUMBER(SEARCH("Em andamento",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>ISNUMBER(SEARCH("Revisar",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>ISNUMBER(SEARCH("Bloqueado",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>ISNUMBER(SEARCH("Cancelado",I2))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>ISNUMBER(SEARCH("Estornado",I2))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation allowBlank="true" error="Informe um dia entre 1 e 30." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A11" type="whole">
       <formula1>1</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha uma condição de consentimento válida." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E11" type="list">
+    <dataValidation allowBlank="true" error="Escolha uma condição de permissão válida." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E11" type="list">
       <formula1>"Não,Sim,Conforme contexto,Não para envio individual"</formula1>
       <formula2>0</formula2>
     </dataValidation>
